--- a/Week 4/pivot-tables.xlsx
+++ b/Week 4/pivot-tables.xlsx
@@ -5,24 +5,25 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\Instructor_material\wk4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab76ec252c957cd7/Desktop/data_bootcamp_folder/instructor_ref/instructor_ref/Week 4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C15448-E856-46D8-B9D1-10752B42F9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{E8C15448-E856-46D8-B9D1-10752B42F9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA3FA6B3-3D63-439C-A0FF-0F81E4117F2F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="796" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" tabRatio="796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="One-dimensional Pivot Table" sheetId="3" r:id="rId2"/>
-    <sheet name="Two-dimensional Pivot Table" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
+    <sheet name="One-dimensional Pivot Table" sheetId="3" r:id="rId3"/>
+    <sheet name="Two-dimensional Pivot Table" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$F$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data!$A$1:$F$214</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId4"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="28">
   <si>
     <t>Country</t>
   </si>
@@ -200,6 +201,1015 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[pivot-tables.xlsx]Sheet3!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Banana</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$5:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>52721</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33775</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36094</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39686</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40050</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>42908</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>95061</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Apple</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$5:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>20634</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24867</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80193</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9082</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10332</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17534</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28615</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Broccoli</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$D$5:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>17953</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12407</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5341</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37197</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4390</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38436</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26715</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Carrots</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$E$5:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>8106</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9104</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21636</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41815</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56284</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$F$3:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Orange</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$F$5:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>8680</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19929</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2256</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8887</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12010</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21744</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30932</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$G$3:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Beans</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$G$5:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>14433</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29905</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7163</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$H$3:$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mango</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>New Zealand</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>United States</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$H$5:$H$12</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>9186</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3767</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8775</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-5BE6-4E64-980E-764AC2A5E710}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1939702960"/>
+        <c:axId val="1937012784"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1939702960"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1937012784"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1937012784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1939702960"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1348,7 +2358,541 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1856,6 +3400,47 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB08B6E7-D8AB-3924-45F9-EA479C948C1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -1890,6 +3475,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4413,7 +6002,218 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49895F86-8F16-49F9-9304-F983F17A832A}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:I12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0" sortType="descending">
+      <items count="8">
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="8">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="3" baseField="1" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -4894,8 +6694,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:I6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -5763,21 +7563,306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8A01EC-53E1-4018-A310-60F5AC05DD8D}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>52721</v>
+      </c>
+      <c r="C5" s="1">
+        <v>20634</v>
+      </c>
+      <c r="D5" s="1">
+        <v>17953</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8106</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8680</v>
+      </c>
+      <c r="G5" s="1">
+        <v>14433</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9186</v>
+      </c>
+      <c r="I5" s="1">
+        <v>131713</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
+        <v>33775</v>
+      </c>
+      <c r="C6" s="1">
+        <v>24867</v>
+      </c>
+      <c r="D6" s="1">
+        <v>12407</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
+        <v>19929</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <v>3767</v>
+      </c>
+      <c r="I6" s="1">
+        <v>94745</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
+        <v>36094</v>
+      </c>
+      <c r="C7" s="1">
+        <v>80193</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5341</v>
+      </c>
+      <c r="E7" s="1">
+        <v>9104</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2256</v>
+      </c>
+      <c r="G7" s="1">
+        <v>680</v>
+      </c>
+      <c r="H7" s="1">
+        <v>7388</v>
+      </c>
+      <c r="I7" s="1">
+        <v>141056</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1">
+        <v>39686</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9082</v>
+      </c>
+      <c r="D8" s="1">
+        <v>37197</v>
+      </c>
+      <c r="E8" s="1">
+        <v>21636</v>
+      </c>
+      <c r="F8" s="1">
+        <v>8887</v>
+      </c>
+      <c r="G8" s="1">
+        <v>29905</v>
+      </c>
+      <c r="H8" s="1">
+        <v>8775</v>
+      </c>
+      <c r="I8" s="1">
+        <v>155168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1">
+        <v>40050</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10332</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4390</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>12010</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1">
+        <v>66782</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>42908</v>
+      </c>
+      <c r="C10" s="1">
+        <v>17534</v>
+      </c>
+      <c r="D10" s="1">
+        <v>38436</v>
+      </c>
+      <c r="E10" s="1">
+        <v>41815</v>
+      </c>
+      <c r="F10" s="1">
+        <v>21744</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5600</v>
+      </c>
+      <c r="I10" s="1">
+        <v>173137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>95061</v>
+      </c>
+      <c r="C11" s="1">
+        <v>28615</v>
+      </c>
+      <c r="D11" s="1">
+        <v>26715</v>
+      </c>
+      <c r="E11" s="1">
+        <v>56284</v>
+      </c>
+      <c r="F11" s="1">
+        <v>30932</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7163</v>
+      </c>
+      <c r="H11" s="1">
+        <v>22363</v>
+      </c>
+      <c r="I11" s="1">
+        <v>267133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1">
+        <v>340295</v>
+      </c>
+      <c r="C12" s="1">
+        <v>191257</v>
+      </c>
+      <c r="D12" s="1">
+        <v>142439</v>
+      </c>
+      <c r="E12" s="1">
+        <v>136945</v>
+      </c>
+      <c r="F12" s="1">
+        <v>104438</v>
+      </c>
+      <c r="G12" s="1">
+        <v>57281</v>
+      </c>
+      <c r="H12" s="1">
+        <v>57079</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1029734</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F214"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -5797,7 +7882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5817,7 +7902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5837,7 +7922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5857,7 +7942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5877,7 +7962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5897,7 +7982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5917,7 +8002,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5937,7 +8022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5957,7 +8042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5977,7 +8062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5997,7 +8082,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6017,7 +8102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6037,7 +8122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6057,7 +8142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6077,7 +8162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6097,7 +8182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6117,7 +8202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6137,7 +8222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6157,7 +8242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6177,7 +8262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6197,7 +8282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6217,7 +8302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6237,7 +8322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6257,7 +8342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6277,7 +8362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6297,7 +8382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6317,7 +8402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6337,7 +8422,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6357,7 +8442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6377,7 +8462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6397,7 +8482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6417,7 +8502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6437,7 +8522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6457,7 +8542,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6477,7 +8562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6497,7 +8582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6517,7 +8602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6537,7 +8622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6557,7 +8642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6577,7 +8662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6597,7 +8682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6617,7 +8702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6637,7 +8722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6657,7 +8742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6677,7 +8762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6697,7 +8782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6717,7 +8802,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6737,7 +8822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6757,7 +8842,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6777,7 +8862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6797,7 +8882,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6817,7 +8902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6837,7 +8922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6857,7 +8942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6877,7 +8962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6897,7 +8982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6917,7 +9002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6937,7 +9022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6957,7 +9042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6977,7 +9062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6997,7 +9082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7017,7 +9102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7037,7 +9122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7057,7 +9142,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7077,7 +9162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7097,7 +9182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7117,7 +9202,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7137,7 +9222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7157,7 +9242,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7177,7 +9262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7197,7 +9282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7217,7 +9302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7237,7 +9322,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7257,7 +9342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7277,7 +9362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7297,7 +9382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7317,7 +9402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7337,7 +9422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7357,7 +9442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7377,7 +9462,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7397,7 +9482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7417,7 +9502,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7437,7 +9522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7457,7 +9542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7477,7 +9562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7497,7 +9582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7517,7 +9602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7537,7 +9622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7557,7 +9642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7577,7 +9662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7597,7 +9682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7617,7 +9702,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7637,7 +9722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7657,7 +9742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7677,7 +9762,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7697,7 +9782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7717,7 +9802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7737,7 +9822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7757,7 +9842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7777,7 +9862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7797,7 +9882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7817,7 +9902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7837,7 +9922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7857,7 +9942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7877,7 +9962,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7897,7 +9982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7917,7 +10002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7937,7 +10022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7957,7 +10042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7977,7 +10062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7997,7 +10082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8017,7 +10102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8037,7 +10122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8057,7 +10142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8077,7 +10162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8097,7 +10182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8117,7 +10202,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8137,7 +10222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8157,7 +10242,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8177,7 +10262,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8197,7 +10282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8217,7 +10302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8237,7 +10322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8257,7 +10342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8277,7 +10362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8297,7 +10382,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8317,7 +10402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8337,7 +10422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8357,7 +10442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8377,7 +10462,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8397,7 +10482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8417,7 +10502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8437,7 +10522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8457,7 +10542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -8477,7 +10562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -8497,7 +10582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -8517,7 +10602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -8537,7 +10622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -8557,7 +10642,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -8577,7 +10662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -8597,7 +10682,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -8617,7 +10702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8637,7 +10722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8657,7 +10742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8677,7 +10762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8697,7 +10782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8717,7 +10802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8737,7 +10822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8757,7 +10842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8777,7 +10862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8797,7 +10882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8817,7 +10902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8837,7 +10922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8857,7 +10942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8877,7 +10962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8897,7 +10982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8917,7 +11002,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8937,7 +11022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8957,7 +11042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8977,7 +11062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8997,7 +11082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9017,7 +11102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9037,7 +11122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9057,7 +11142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9077,7 +11162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -9097,7 +11182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9117,7 +11202,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9137,7 +11222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9157,7 +11242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9177,7 +11262,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9197,7 +11282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9217,7 +11302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9237,7 +11322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9257,7 +11342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9277,7 +11362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9297,7 +11382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9317,7 +11402,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9337,7 +11422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9357,7 +11442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9377,7 +11462,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9397,7 +11482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9417,7 +11502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9437,7 +11522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9457,7 +11542,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9477,7 +11562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9497,7 +11582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9517,7 +11602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9537,7 +11622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9557,7 +11642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9577,7 +11662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9597,7 +11682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9617,7 +11702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9637,7 +11722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9657,7 +11742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9677,7 +11762,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9697,7 +11782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -9717,7 +11802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -9737,7 +11822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -9757,7 +11842,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -9777,7 +11862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -9797,7 +11882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -9817,7 +11902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -9837,7 +11922,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -9857,7 +11942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -9877,7 +11962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -9897,7 +11982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -9917,7 +12002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -9937,7 +12022,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -9957,7 +12042,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -9977,7 +12062,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -9997,7 +12082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10017,7 +12102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10037,7 +12122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10063,16 +12148,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -10080,7 +12165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
@@ -10088,7 +12173,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -10096,7 +12181,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
@@ -10104,7 +12189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -10112,7 +12197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -10120,7 +12205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -10128,7 +12213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
@@ -10136,7 +12221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -10144,7 +12229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>24</v>
       </c>
@@ -10157,23 +12242,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" customWidth="1"/>
+    <col min="4" max="4" width="6.36328125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" customWidth="1"/>
+    <col min="8" max="8" width="7.453125" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -10181,7 +12266,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -10189,7 +12274,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
@@ -10218,7 +12303,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -10247,7 +12332,7 @@
         <v>267133</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
